--- a/backend/static/ProjectAuthorsTemplate.xlsx
+++ b/backend/static/ProjectAuthorsTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waqar\Documents\Github Projects\Automatic-Data-Analytics-with-NLP\backend\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464E7D7F-E6C2-40EF-B6C9-03136C861B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123C5F87-B34F-41D8-ADA1-BA5C2887CAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Name</t>
   </si>
@@ -88,9 +88,6 @@
     <t>https://github.com/INSHPREET</t>
   </si>
   <si>
-    <t>Dr. Aashiq Hussain  Dar</t>
-  </si>
-  <si>
     <t>Director In-Charge, NIELIT</t>
   </si>
   <si>
@@ -128,6 +125,21 @@
   </si>
   <si>
     <t>https://www.linkedin.com/in/dr-syed-nisar-bukhari-76b8606</t>
+  </si>
+  <si>
+    <t>Miss. Nida Nek</t>
+  </si>
+  <si>
+    <t>AI/ML Research Associate, NIELIT</t>
+  </si>
+  <si>
+    <t>Dr. Ashaq Hussain Dar,</t>
+  </si>
+  <si>
+    <t>Miss Nida Nek is an Associate AI/ML Researcher at NIELIT, recognized for her significant support in the development of this project. Through her valuable suggestions, feedback, and reviews, she has contributed immensely to the project's progress. Her expertise was instrumental in the implementation of AI components, helping to bridge research and practical application within the team.</t>
+  </si>
+  <si>
+    <t>Er. Sarfaraz Sir is the Software Development Incharge at NIELIT, holding an M.Sc. in IT and extensive experience in deploying numerous MeitY projects. His valuable input to this project includes implementing the chatbot integration via OpenRouter and assisting in designing the overall workflow. His expertise in software development and project deployment has been pivotal in enhancing the technical architecture and functionality of the project.</t>
   </si>
 </sst>
 </file>
@@ -534,13 +546,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD2D2DAE-F4B0-40A3-8FBF-9BEF737D3860}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="19.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -561,72 +574,89 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/backend/static/ProjectAuthorsTemplate.xlsx
+++ b/backend/static/ProjectAuthorsTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waqar\Documents\Github Projects\Automatic-Data-Analytics-with-NLP\backend\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123C5F87-B34F-41D8-ADA1-BA5C2887CAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5822BC04-439D-4AEE-A108-C4AEDDBFFEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>Name</t>
   </si>
@@ -94,9 +94,6 @@
     <t>Dr. Syed Nisar Bukhari</t>
   </si>
   <si>
-    <t>Project Supervisor, NIELIT</t>
-  </si>
-  <si>
     <t>Software Development Incharge, NIELIT</t>
   </si>
   <si>
@@ -121,9 +118,6 @@
     <t>nisar.jpg</t>
   </si>
   <si>
-    <t>Dr. Syed Nisar Bukhari is a Machine Learning researcher and academician with a strong focus on interdisciplinary research in Artificial Intelligence and Machine Learning. Currently serving as a Project Supervisor and Academic Incharge at NIELIT Srinagar, he plays a key role in guiding research initiatives and academic programs. His work bridges theory and application across diverse domains, contributing to the advancement of AI/ML technologies.</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/dr-syed-nisar-bukhari-76b8606</t>
   </si>
   <si>
@@ -140,6 +134,15 @@
   </si>
   <si>
     <t>Er. Sarfaraz Sir is the Software Development Incharge at NIELIT, holding an M.Sc. in IT and extensive experience in deploying numerous MeitY projects. His valuable input to this project includes implementing the chatbot integration via OpenRouter and assisting in designing the overall workflow. His expertise in software development and project deployment has been pivotal in enhancing the technical architecture and functionality of the project.</t>
+  </si>
+  <si>
+    <t>inshpreet.jpg</t>
+  </si>
+  <si>
+    <t>Project Supervisor &amp; HOD, NIELIT</t>
+  </si>
+  <si>
+    <t>Dr. Syed Nisar Hussain Bukhari is a Machine Learning researcher and academician with a strong focus on interdisciplinary research in Artificial Intelligence &amp; Machine Learning. He currently serves as Scientist-D and HoD at NIELIT, where he leads academic and research initiatives. With over 12 years of experience, he has published extensively and contributed to books with CRC Press. As a Project Supervisor, he is actively guiding our research project, providing valuable expertise and mentorship in advancing real-world AI/ML applications.</t>
   </si>
 </sst>
 </file>
@@ -524,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -547,24 +550,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD2D2DAE-F4B0-40A3-8FBF-9BEF737D3860}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="113.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="52.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="23.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -574,66 +577,66 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>37</v>
+      <c r="C3" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>36</v>
+      <c r="C4" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
@@ -642,21 +645,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
